--- a/artfynd/A 1100-2024 artfynd.xlsx
+++ b/artfynd/A 1100-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 1100-2024 artfynd.xlsx
+++ b/artfynd/A 1100-2024 artfynd.xlsx
@@ -902,12 +902,7 @@
         <v>81769935</v>
       </c>
       <c r="B4" t="n">
-        <v>5135</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5196</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -939,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>613025.7704626948</v>
+        <v>613026</v>
       </c>
       <c r="R4" t="n">
-        <v>6744762.143407275</v>
+        <v>6744762</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,19 +967,9 @@
           <t>2019-09-26</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2019-09-26</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">

--- a/artfynd/A 1100-2024 artfynd.xlsx
+++ b/artfynd/A 1100-2024 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>81769935</v>
       </c>
       <c r="B4" t="n">
-        <v>5196</v>
+        <v>5197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 1100-2024 artfynd.xlsx
+++ b/artfynd/A 1100-2024 artfynd.xlsx
@@ -994,7 +994,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Barbara Kühn, Kajsa Mattsson, Anna Broberg</t>
+          <t>Anna Broberg, Kajsa Mattsson, Barbara Kühn</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 1100-2024 artfynd.xlsx
+++ b/artfynd/A 1100-2024 artfynd.xlsx
@@ -994,7 +994,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anna Broberg, Kajsa Mattsson, Barbara Kühn</t>
+          <t>Barbara Kühn, Kajsa Mattsson, Anna Broberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 1100-2024 artfynd.xlsx
+++ b/artfynd/A 1100-2024 artfynd.xlsx
@@ -675,19 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>81770320</v>
+        <v>81770316</v>
       </c>
       <c r="B2" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>613045.1367788669</v>
+        <v>612906</v>
       </c>
       <c r="R2" t="n">
-        <v>6744768.126366071</v>
+        <v>6744714</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2019-09-26</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-09-26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>81769963</v>
+        <v>81770320</v>
       </c>
       <c r="B3" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>613022.1876557252</v>
+        <v>613045</v>
       </c>
       <c r="R3" t="n">
-        <v>6744751.779434077</v>
+        <v>6744768</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +840,9 @@
           <t>2019-09-26</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-09-26</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>81769935</v>
+        <v>81770002</v>
       </c>
       <c r="B4" t="n">
-        <v>5197</v>
+        <v>91930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>105930</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>613026</v>
+        <v>612919</v>
       </c>
       <c r="R4" t="n">
-        <v>6744762</v>
+        <v>6744918</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -970,11 +940,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2019-09-26</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>gnagspår</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,37 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>81770316</v>
+        <v>81769963</v>
       </c>
       <c r="B5" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1041,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>612906.0498434218</v>
+        <v>613022</v>
       </c>
       <c r="R5" t="n">
-        <v>6744713.933230401</v>
+        <v>6744752</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1074,19 +1034,9 @@
           <t>2019-09-26</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2019-09-26</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,37 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>81770053</v>
+        <v>81769935</v>
       </c>
       <c r="B6" t="n">
-        <v>90697</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5449</v>
+        <v>105930</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1153,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>613030.1291927886</v>
+        <v>613026</v>
       </c>
       <c r="R6" t="n">
-        <v>6744778.877427729</v>
+        <v>6744762</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1186,19 +1131,14 @@
           <t>2019-09-26</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2019-09-26</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>gnagspår</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 1100-2024 artfynd.xlsx
+++ b/artfynd/A 1100-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81770316</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81770320</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81770002</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81769963</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,8 +1187,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81769935</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>